--- a/per-stock/CLSK/financials.xlsx
+++ b/per-stock/CLSK/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3364138752</v>
+        <v>4423932416</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4894574080</v>
+        <v>5954367488</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -578,7 +587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-21.317072</v>
+        <v>-23.779308</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -593,7 +602,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.546846</v>
+        <v>5.979224</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -713,11 +722,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-300704512</v>
+        <v>-1072203000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -743,7 +752,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13.11</v>
+        <v>17.24</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -787,6 +796,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D57</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C57</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B57</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B55:E55)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D55</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C55</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B55</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B53:E53)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D43</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C43</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B43</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B44:E44)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B7:E7)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B6</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D4/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C4/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B4/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B4/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -842,10 +1322,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>41170292</v>
+        <v>-117370</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>-19060650</v>
+        <v>-42879480</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>-1157520</v>
@@ -882,10 +1362,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>338809000</v>
+        <v>764455000</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>105396000</v>
+        <v>218819000</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>-2086000</v>
@@ -902,10 +1382,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>424436000</v>
+        <v>-1210000</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>-90765000</v>
+        <v>-204188000</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>-5512000</v>
@@ -922,10 +1402,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>424436000</v>
+        <v>-1210000</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>-90765000</v>
+        <v>-204188000</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>-5512000</v>
@@ -1102,10 +1582,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-18801708</v>
+        <v>365556630</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>-74072650</v>
+        <v>15531520</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>-129364520</v>
@@ -1462,10 +1942,10 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>93382000</v>
+        <v>519028000</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1475000</v>
+        <v>114898000</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>11000</v>
@@ -1582,10 +2062,10 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>424100000</v>
+        <v>-1546000</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>112458000</v>
+        <v>-965000</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>1098000</v>
@@ -1968,13 +2448,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1984,6 +2464,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1994,30 +2475,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -2030,21 +2516,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-320950</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-18188324</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>13425300</v>
-      </c>
       <c r="D2" s="3" t="n">
-        <v>17692290</v>
+        <v>-530460</v>
       </c>
       <c r="E2" s="3" t="n">
+        <v>-38676</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>-52731</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>8014903.139746</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2053,21 +2540,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.077</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.066</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>0.021</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>0.036003</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2076,21 +2564,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-257461000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-63907000</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>63355000</v>
-      </c>
       <c r="D4" s="3" t="n">
-        <v>105766000</v>
+        <v>129811000</v>
       </c>
       <c r="E4" s="3" t="n">
+        <v>374417000</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>-59156000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>101177000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2099,21 +2588,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-12838000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-236212000</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>63930000</v>
-      </c>
       <c r="D5" s="3" t="n">
-        <v>268065000</v>
+        <v>-2526000</v>
       </c>
       <c r="E5" s="3" t="n">
+        <v>-586000</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>-2511000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>222619000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2122,21 +2612,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-12838000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-236212000</v>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>63930000</v>
-      </c>
       <c r="D6" s="3" t="n">
-        <v>268065000</v>
+        <v>-2526000</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>-586000</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>-2511000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>222619000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2145,21 +2636,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-378343000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-378711000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-925000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>257390000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-138792000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>246791000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2168,21 +2660,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>115881000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>106311000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>108325000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>94880000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>78901000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>66229000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2191,21 +2684,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>106613000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>119406000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>149116000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>106526000</v>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>85424000</v>
-      </c>
       <c r="F9" s="3" t="n">
-        <v>91159000</v>
+        <v>100679000</v>
       </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2214,21 +2708,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-270299000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-300119000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>127285000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>373831000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>-61667000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>323796000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2237,21 +2732,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-386180000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-406430000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>18960000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>278951000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-140568000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>257567000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2260,21 +2756,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>1018000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-1511000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-4775000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-3099000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>747000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-83000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2283,21 +2780,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>2054000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>3696000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>5055000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>3454000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>1267000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>1559000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2306,21 +2804,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>3072000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>2185000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>280000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>355000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>2014000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>1476000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2329,21 +2828,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-365825950</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-160687324</v>
       </c>
-      <c r="C15" s="3" t="n">
-        <v>-51429700</v>
-      </c>
       <c r="D15" s="3" t="n">
-        <v>7017290</v>
+        <v>1070540</v>
       </c>
       <c r="E15" s="3" t="n">
+        <v>257937324</v>
+      </c>
+      <c r="F15" s="3" t="n">
         <v>-136333731</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>32186903.139746</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2352,21 +2852,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-378343000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-378711000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-925000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>257390000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-138792000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>246791000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2375,21 +2876,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>249982000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>249727000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>286745000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>220976000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>194299000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>171327000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2398,21 +2900,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-345679000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-316554000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>834000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>246163000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-138024000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>209976000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2421,19 +2924,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>267827913</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>281474949</v>
       </c>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n">
         <v>325594451</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>280853882</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="G19" s="3" t="n">
         <v>297887140</v>
       </c>
-      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2442,19 +2948,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>267827913</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>281474949</v>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n">
         <v>280997649</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>280853882</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="G20" s="3" t="n">
         <v>284549900</v>
       </c>
-      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2463,19 +2972,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>-1.35</v>
       </c>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-0.49</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="G21" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2484,19 +2996,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-1.35</v>
       </c>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-0.49</v>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="G22" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2505,730 +3020,789 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-408343000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-378711000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-1321000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>251787000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-138792000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>241650000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Net Income Common Stockholders</t>
+          <t>Average Dilution Earnings</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-378711000</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>-1321000</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>251787000</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>-138792000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n">
-        <v>241650000</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Preferred Stock Dividends</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n"/>
+          <t>Net Income Common Stockholders</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>-408343000</v>
+      </c>
       <c r="C25" s="3" t="n">
-        <v>396000</v>
+        <v>-378711000</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>5603000</v>
-      </c>
-      <c r="E25" s="3" t="n"/>
+        <v>-1321000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>251787000</v>
+      </c>
       <c r="F25" s="3" t="n">
-        <v>5141000</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>1000</v>
-      </c>
+        <v>-138792000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Net Income</t>
+          <t>Preferred Stock Dividends</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-378711000</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>-925000</v>
-      </c>
+        <v>30000000</v>
+      </c>
+      <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="n">
-        <v>257390000</v>
+        <v>396000</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-138792000</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>246791000</v>
-      </c>
-      <c r="G26" s="3" t="n"/>
+        <v>5603000</v>
+      </c>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n">
+        <v>5141000</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Net Income Including Noncontrolling Interests</t>
+          <t>Net Income</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-378343000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-378711000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-925000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>257390000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-138792000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>246791000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Net Income Discontinuous Operations</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>Net Income Including Noncontrolling Interests</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>-378343000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>-378711000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>-925000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>257390000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>-138792000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Net Income Continuous Operations</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>-378711000</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>-925000</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>257390000</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>-138792000</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>246791000</v>
-      </c>
+          <t>Net Income Discontinuous Operations</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tax Provision</t>
+          <t>Net Income Continuous Operations</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-31415000</v>
+        <v>-378343000</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>14830000</v>
+        <v>-378711000</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>18107000</v>
+        <v>-925000</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-3043000</v>
+        <v>257390000</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>9217000</v>
+        <v>-138792000</v>
       </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pretax Income</t>
+          <t>Tax Provision</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-410126000</v>
+        <v>-9891000</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>13905000</v>
+        <v>-31415000</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>275497000</v>
+        <v>14830000</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-141835000</v>
+        <v>18107000</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>256008000</v>
+        <v>-3043000</v>
       </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Other Income Expense</t>
+          <t>Pretax Income</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-340068000</v>
+        <v>-388234000</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>81773000</v>
+        <v>-410126000</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>300928000</v>
+        <v>13905000</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>-129995000</v>
+        <v>275497000</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>265112000</v>
+        <v>-141835000</v>
       </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Other Non Operating Income Expenses</t>
+          <t>Other Income Expense</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>-103856000</v>
+        <v>-275678000</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>17843000</v>
+        <v>-340068000</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>32863000</v>
+        <v>81773000</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-127484000</v>
+        <v>300928000</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>42493000</v>
+        <v>-129995000</v>
       </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Special Income Charges</t>
+          <t>Other Non Operating Income Expenses</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>-1175000</v>
+        <v>-262840000</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>-2529000</v>
+        <v>-103856000</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>-156000</v>
+        <v>84299000</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>2230000</v>
+        <v>301514000</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>791000</v>
+        <v>-127484000</v>
       </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Gain On Sale Of Ppe</t>
+          <t>Special Income Charges</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>223000</v>
+        <v>-7998000</v>
       </c>
       <c r="C35" s="3" t="n">
+        <v>-1175000</v>
+      </c>
+      <c r="D35" s="3" t="n">
         <v>-2529000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-156000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>2230000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>791000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Write Off</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n"/>
+          <t>Gain On Sale Of Ppe</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>-3990000</v>
+      </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>223000</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>-2529000</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="3" t="n">
-        <v>320000</v>
-      </c>
+        <v>-156000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>2230000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Impairment Of Capital Assets</t>
+          <t>Write Off</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>1398000</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>4008000</v>
+      </c>
+      <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E37" s="3" t="n"/>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="F37" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>7806000</v>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n">
+        <v>320000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Restructuring And Mergern Acquisition</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="n"/>
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n"/>
-      <c r="G38" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>Impairment Of Capital Assets</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>1398000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Gain On Sale Of Security</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>-235037000</v>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>66459000</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>268221000</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>-4741000</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>221828000</v>
-      </c>
+          <t>Restructuring And Mergern Acquisition</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Net Non Operating Interest Income Expense</t>
+          <t>Gain On Sale Of Security</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>-1511000</v>
+        <v>-4840000</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>-4775000</v>
+        <v>-235037000</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>-3099000</v>
+        <v>3000</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>747000</v>
+        <v>-430000</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>-83000</v>
+        <v>-4741000</v>
       </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Interest Expense Non Operating</t>
+          <t>Net Non Operating Interest Income Expense</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>3696000</v>
+        <v>1018000</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>5055000</v>
+        <v>-1511000</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>3454000</v>
+        <v>-4775000</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1267000</v>
+        <v>-3099000</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>1559000</v>
+        <v>747000</v>
       </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Interest Income Non Operating</t>
+          <t>Interest Expense Non Operating</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>2185000</v>
+        <v>2054000</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>280000</v>
+        <v>3696000</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>355000</v>
+        <v>5055000</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>2014000</v>
+        <v>3454000</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1476000</v>
+        <v>1267000</v>
       </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Operating Income</t>
+          <t>Interest Income Non Operating</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>-68547000</v>
+        <v>3072000</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>-63093000</v>
+        <v>2185000</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>-22332000</v>
+        <v>280000</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>-12587000</v>
+        <v>355000</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>-9021000</v>
+        <v>2014000</v>
       </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Operating Expense</t>
+          <t>Operating Income</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>130321000</v>
+        <v>-113574000</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>137629000</v>
+        <v>-68547000</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>114450000</v>
+        <v>-63093000</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>108875000</v>
+        <v>-22332000</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>80168000</v>
+        <v>-12587000</v>
       </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Other Taxes</t>
+          <t>Operating Expense</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>3162000</v>
-      </c>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="n"/>
+        <v>143369000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>130321000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>137629000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>114450000</v>
+      </c>
       <c r="F45" s="3" t="n">
-        <v>0</v>
+        <v>93620000</v>
       </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Depreciation Amortization Depletion Income Statement</t>
+          <t>Other Taxes</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>106311000</v>
+        <v>1731000</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>108325000</v>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>94880000</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>78901000</v>
-      </c>
+        <v>3162000</v>
+      </c>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="n">
-        <v>66229000</v>
-      </c>
-      <c r="G46" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Depreciation And Amortization In Income Statement</t>
+          <t>Depreciation Amortization Depletion Income Statement</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>115881000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>106311000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>108325000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>94880000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>78901000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>66229000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Selling General And Administration</t>
+          <t>Depreciation And Amortization In Income Statement</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>20848000</v>
+        <v>115881000</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>18182000</v>
+        <v>106311000</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>19570000</v>
+        <v>108325000</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>29974000</v>
+        <v>94880000</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13939000</v>
+        <v>78901000</v>
       </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>General And Administrative Expense</t>
+          <t>Selling General And Administration</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>25757000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>20848000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>18182000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>19570000</v>
       </c>
-      <c r="E49" s="3" t="n">
-        <v>29974000</v>
-      </c>
       <c r="F49" s="3" t="n">
-        <v>13939000</v>
+        <v>14719000</v>
       </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Other Gand A</t>
+          <t>General And Administrative Expense</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>25757000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>20848000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>18182000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>19570000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>14719000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>13939000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Salaries And Wages</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="n"/>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="3" t="n"/>
+          <t>Other Gand A</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>25757000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>20848000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>18182000</v>
+      </c>
       <c r="E51" s="3" t="n">
-        <v>15255000</v>
-      </c>
-      <c r="F51" s="3" t="n"/>
+        <v>19570000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>14719000</v>
+      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="n">
-        <v>61774000</v>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>74536000</v>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>92118000</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>96288000</v>
-      </c>
+          <t>Salaries And Wages</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n"/>
+      <c r="C52" s="3" t="n"/>
+      <c r="D52" s="3" t="n"/>
+      <c r="E52" s="3" t="n"/>
       <c r="F52" s="3" t="n">
-        <v>71147000</v>
+        <v>15255000</v>
       </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cost Of Revenue</t>
+          <t>Gross Profit</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>119406000</v>
+        <v>29795000</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>149116000</v>
+        <v>61774000</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>106526000</v>
+        <v>74536000</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>85424000</v>
+        <v>92118000</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>91159000</v>
+        <v>81033000</v>
       </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Total Revenue</t>
+          <t>Cost Of Revenue</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>181180000</v>
+        <v>106613000</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>223652000</v>
+        <v>119406000</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>198644000</v>
+        <v>149116000</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>181712000</v>
+        <v>106526000</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>162306000</v>
+        <v>100679000</v>
       </c>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>136408000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>181180000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>223652000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>198644000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>181712000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>Operating Revenue</t>
         </is>
       </c>
-      <c r="B55" s="3" t="n">
+      <c r="B56" s="3" t="n">
+        <v>136408000</v>
+      </c>
+      <c r="C56" s="3" t="n">
         <v>181180000</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="D56" s="3" t="n">
         <v>223652000</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="E56" s="3" t="n">
         <v>198644000</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="F56" s="3" t="n">
         <v>181712000</v>
       </c>
-      <c r="F55" s="3" t="n">
-        <v>162306000</v>
-      </c>
-      <c r="G55" s="3" t="n"/>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4824,7 +5398,1747 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>42365391</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>42365391</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>11759935</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>11759935</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>11759935</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Preferred Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>256599199</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>255749498</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>284327598</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>281063551</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>280900178</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>298964590</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>298114889</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>296087533</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>292823486</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>292660113</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1530394000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1331194000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>778190000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>785784000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>550178000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1790681000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1789291000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>824437000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>820337000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>647160000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>850209000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1245689000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>2037618000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>2011121000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1751295000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>2776839000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>3171545000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>2996281000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>2967223000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>2537649000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>965969000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1331149000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1004276000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>933321000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>838181000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>850211000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1245691000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>2037620000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>2011123000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1751297000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n">
+        <v>3281000</v>
+      </c>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n">
+        <v>997000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>986158000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1382254000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>2175125000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>2146886000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1890489000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Preferred Stock Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>2774356000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>3169015000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>2819713000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>2790801000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>2532231000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>986160000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1382256000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>2175127000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>2146888000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1890491000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>986160000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>1382256000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>2175127000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>2146888000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>1890491000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>3173000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>3396000</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>450000</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>418000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n">
+        <v>3173000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>3396000</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>450000</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>418000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>608190000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>608270000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>145000000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>145000000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>145000000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>-912948000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>-504605000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>-125894000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-124573000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>-376360000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>2506997000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>2494831000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2445723000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>2412993000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>2408160000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>301000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>298000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>295000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>295000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>299000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>298000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>296000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>293000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>293000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1927341000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>1943923000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1008504000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>954929000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>766507000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>1794273000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1804426000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>692739000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>678110000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>657195000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>2511000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>4210000</v>
+      </c>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n">
+        <v>3423000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>3521000</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>4618000</v>
+      </c>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>3566000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>13457000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>44872000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>30774000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>11934000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>3566000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>13457000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>44872000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>30774000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>11934000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>1788196000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>1786759000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>647867000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>643913000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>641740000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n">
+        <v>3281000</v>
+      </c>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n">
+        <v>997000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>1788196000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>1786759000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>644586000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>643913000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>641740000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>133068000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>139497000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>315765000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>276819000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>109312000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>10994000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>11160000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>6096000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>6830000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>4596000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>2485000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>2532000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>176570000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>176424000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>5420000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>2485000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>2532000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>176570000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>176424000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>5420000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>119589000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>125805000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>133099000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>93565000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>99296000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>30552000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>103689000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>117544000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>64492000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>87906000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>89037000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>22116000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>15555000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>29073000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>11390000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Dividends Payable</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>396000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>5603000</v>
+      </c>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n">
+        <v>5141000</v>
+      </c>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>70979000</v>
+      </c>
+      <c r="C42" s="3" t="n"/>
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3" t="n"/>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>18058000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>22116000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>15159000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>23470000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>11390000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>2913501000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>3326179000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>3183631000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>3101817000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>2656998000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>1814464000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>1855533000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>1863590000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1891677000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>1709505000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>63384000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>54601000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>23497000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>23065000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>23400000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>138774000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>171924000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>222614000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>202687000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>146945000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Investmentin Financial Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>138774000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>171924000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>222614000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>202687000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>146945000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>135949000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>136565000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>137507000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>135765000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>139194000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>4291000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>4907000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>5849000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>6955000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>6978000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>131658000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>131658000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>131658000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>128810000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>132216000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>1476357000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>1492443000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>1479972000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>1530160000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1399966000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>-746466000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>-639440000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>-559943000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>-483305000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>-371017000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>2222823000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>2131883000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>2039915000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>2013465000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1770983000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>2941000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>2941000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>2941000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>2941000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>2471000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>181424000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>162167000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>124825000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>213331000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>161648000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>345124000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>322717000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>300091000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>292237000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>252741000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>24661000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>22728000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>19604000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>18755000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>18483000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>100633000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>96872000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>96400000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>91783000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>79764000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>138231000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>109081000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>49236000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>48989000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>45155000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>1429809000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>1415377000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>1446818000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>1345429000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>1210721000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>1099037000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>1470646000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>1320041000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>1210140000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>947493000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>47651000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>35121000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>11875000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>11319000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>10418000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Hedging Assets Current</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>1499000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>233000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>7843000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>72000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Assets Held For Sale Current</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3" t="n"/>
+      <c r="D65" s="3" t="n"/>
+      <c r="E65" s="3" t="n"/>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Restricted Cash</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>3213000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>3192000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>3490000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>3462000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>3435000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>111940000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>144163000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>294648000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>271491000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>111940000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>144163000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>294648000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>271491000</v>
+      </c>
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n">
+        <v>77827000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Notes Receivable</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="3" t="n"/>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>60919000</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>934734000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>1288170000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>1009795000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>916025000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>933568000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>674447000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>830073000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>966829000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>881472000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>836586000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>260287000</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>458097000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>42966000</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>34553000</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>96982000</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6252,13 +8566,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6268,6 +8582,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6278,30 +8593,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -6314,21 +8634,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-173421000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-198063000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-548296000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-152423000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-146375000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-176811000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6337,11 +8658,11 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-460000000</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" s="3" t="n">
         <v>0</v>
       </c>
@@ -6349,9 +8670,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-145000000</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6360,21 +8682,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-669000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-251131000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-77458000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-4082000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-2281000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-52184000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6383,21 +8706,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>1209086000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>77000000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>176500000</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="F5" s="3" t="n">
-        <v>635695000</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6415,12 +8739,13 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>186807000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6429,21 +8754,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-37594000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-36928000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-428887000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-42535000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-34092000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>-57359000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6452,21 +8778,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>352000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>2396000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>4304000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>2686000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>490000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>1399000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6475,21 +8802,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>263500000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>461289000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>46456000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>38015000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>100417000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>280007000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6498,21 +8826,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>461289000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>46456000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>38015000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>100417000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>280007000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>124278000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6521,21 +8850,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-197789000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>414833000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>8441000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-62402000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-179590000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>155729000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6544,21 +8874,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-31367000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>496378000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-7648000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>172763000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-7377000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>531128000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6571,7 +8902,8 @@
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n">
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6582,21 +8914,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-31367000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>496378000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-7648000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>172763000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-7377000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>531128000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6605,21 +8938,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-812000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-2113000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-2010000</v>
       </c>
-      <c r="D15" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-94300000</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6628,21 +8962,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>114000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>932000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>423000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>345000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>44000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>110000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6651,21 +8986,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>-30000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>-396000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>-5603000</v>
       </c>
-      <c r="D17" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="n">
         <v>-5141000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6674,21 +9010,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-30000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-396000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-5603000</v>
       </c>
-      <c r="D18" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="n">
         <v>-5141000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6697,21 +9034,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>-460000000</v>
       </c>
-      <c r="C19" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>41807000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6720,11 +9058,11 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>-460000000</v>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D20" s="3" t="n">
         <v>0</v>
       </c>
@@ -6732,9 +9070,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-145000000</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6752,12 +9091,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>186807000</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6766,21 +9106,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-669000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>957955000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-458000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>172418000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-2281000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>583511000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6789,21 +9130,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-669000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>957955000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-458000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>172418000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-2281000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>583511000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6812,21 +9154,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-669000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-251131000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-77458000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-4082000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-2281000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>-52184000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6835,21 +9178,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>1209086000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>77000000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>176500000</v>
       </c>
-      <c r="E25" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="F25" s="3" t="n">
-        <v>635695000</v>
+        <v>0</v>
       </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6858,21 +9202,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-30595000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>79590000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>135498000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-125277000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-59930000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>-255947000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6885,7 +9230,8 @@
       <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n">
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6896,21 +9242,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>-30595000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>79590000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>135498000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>-125277000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>-59930000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>-255947000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6919,21 +9266,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-13246000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-50403000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>418569000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-128531000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-61860000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-191894000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6942,21 +9290,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>8570000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>188528000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>181745000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>45882000</v>
       </c>
-      <c r="E30" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="F30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6965,21 +9314,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>187367000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>189400000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>259777000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>128034000</v>
       </c>
-      <c r="E31" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="F31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6988,17 +9338,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-178797000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-872000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>-78032000</v>
       </c>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="n"/>
+      <c r="E32" s="3" t="n">
+        <v>-82152000</v>
+      </c>
       <c r="F32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7007,21 +9362,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>11675000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-21607000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-34518000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-1504000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>37433000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>-8105000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7030,15 +9386,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n">
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n">
         <v>-41421000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>-91000</v>
       </c>
-      <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n"/>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7047,21 +9404,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>8314000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-21607000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>6903000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-1413000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>-5490000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>-8105000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7070,21 +9428,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-37594000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>-36928000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>-430298000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>-41124000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-35503000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>-55948000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7092,16 +9451,17 @@
           <t>Sale Of PPE</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="3" t="n"/>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="D37" s="3" t="n"/>
       <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n">
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n">
         <v>1411000</v>
       </c>
-      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7110,21 +9470,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>-37594000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>-36928000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>-428887000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>-42535000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>-34092000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>-57359000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7133,21 +9494,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>-135827000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>-161135000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>-119409000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>-109888000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>-112283000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>-119452000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7156,9 +9518,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="C40" s="3" t="n"/>
       <c r="D40" s="3" t="n">
         <v>0</v>
       </c>
@@ -7169,6 +9529,9 @@
         <v>0</v>
       </c>
       <c r="G40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3" t="n">
         <v>-70000</v>
       </c>
     </row>
@@ -7179,21 +9542,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>-135827000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>-161135000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>-119409000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>-109888000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>-112283000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>-119452000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7202,21 +9566,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>9127000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>-30905000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>22473000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>7352000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>7757000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>-18079000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7225,21 +9590,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>-456000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>-425000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>-416000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>-315000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>-193000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>-148000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7247,16 +9613,17 @@
           <t>Change In Other Current Assets</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n">
+      <c r="B44" s="3" t="n"/>
+      <c r="C44" s="3" t="n">
         <v>-15211000</v>
       </c>
-      <c r="C44" s="3" t="n"/>
       <c r="D44" s="3" t="n"/>
       <c r="E44" s="3" t="n"/>
-      <c r="F44" s="3" t="n">
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n">
         <v>-12477000</v>
       </c>
-      <c r="G44" s="3" t="n">
+      <c r="H44" s="3" t="n">
         <v>289693000</v>
       </c>
     </row>
@@ -7267,21 +9634,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>-8274000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>-16547000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>31222000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>9926000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>-3700000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>-4654000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7290,21 +9658,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>2646000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>1278000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>-1171000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>-2259000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>-827000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>-800000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7313,21 +9682,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>-160438000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>-178379000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>549749000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>-192686000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>-190384000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>-161519000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7336,21 +9706,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>12054000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>12132000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>34726000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>4487000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>3101000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>3021000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7359,17 +9730,20 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>262945000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>350452000</v>
       </c>
-      <c r="C49" s="3" t="n"/>
       <c r="D49" s="3" t="n"/>
-      <c r="E49" s="3" t="n">
-        <v>218206000</v>
-      </c>
+      <c r="E49" s="3" t="n"/>
       <c r="F49" s="3" t="n">
+        <v>127667000</v>
+      </c>
+      <c r="G49" s="3" t="n">
         <v>-260699000</v>
       </c>
-      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7378,11 +9752,11 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>4008000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>1398000</v>
       </c>
-      <c r="C50" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D50" s="3" t="n">
         <v>0</v>
       </c>
@@ -7393,6 +9767,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7401,21 +9776,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>-9891000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>-31415000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>14830000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>18108000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>-3044000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>9217000</v>
-      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7424,21 +9800,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>-9891000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>-31415000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>14830000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>18108000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>-3044000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>9217000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7447,21 +9824,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>115881000</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>106311000</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>108325000</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>94880000</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="F53" s="3" t="n">
         <v>78901000</v>
       </c>
-      <c r="F53" s="3" t="n">
-        <v>66229000</v>
-      </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7470,21 +9848,22 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
+        <v>115881000</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>106311000</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>108325000</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>94880000</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="F54" s="3" t="n">
         <v>78901000</v>
       </c>
-      <c r="F54" s="3" t="n">
-        <v>66229000</v>
-      </c>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7493,21 +9872,22 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
+        <v>617000</v>
+      </c>
+      <c r="C55" s="3" t="n">
         <v>942000</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="D55" s="3" t="n">
         <v>1106000</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>1022000</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="F55" s="3" t="n">
         <v>968000</v>
       </c>
-      <c r="F55" s="3" t="n">
-        <v>1104000</v>
-      </c>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7516,21 +9896,22 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
+        <v>617000</v>
+      </c>
+      <c r="C56" s="3" t="n">
         <v>942000</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="D56" s="3" t="n">
         <v>1106000</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="E56" s="3" t="n">
         <v>1022000</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="F56" s="3" t="n">
         <v>968000</v>
       </c>
-      <c r="F56" s="3" t="n">
-        <v>1104000</v>
-      </c>
       <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7539,21 +9920,22 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
+        <v>115265000</v>
+      </c>
+      <c r="C57" s="3" t="n">
         <v>105368000</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="D57" s="3" t="n">
         <v>107219000</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="E57" s="3" t="n">
         <v>93858000</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="F57" s="3" t="n">
         <v>77933000</v>
       </c>
-      <c r="F57" s="3" t="n">
-        <v>65125000</v>
-      </c>
       <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7562,21 +9944,22 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
+        <v>8830000</v>
+      </c>
+      <c r="C58" s="3" t="n">
         <v>-12018000</v>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="D58" s="3" t="n">
         <v>-422941000</v>
       </c>
-      <c r="D58" s="3" t="n">
-        <v>-341912000</v>
-      </c>
       <c r="E58" s="3" t="n">
-        <v>-88028000</v>
+        <v>-432451000</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>-4413000</v>
+        <v>2511000</v>
       </c>
       <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7585,21 +9968,22 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
+        <v>4840000</v>
+      </c>
+      <c r="C59" s="3" t="n">
         <v>-11795000</v>
       </c>
-      <c r="C59" s="3" t="n">
+      <c r="D59" s="3" t="n">
         <v>-333280000</v>
       </c>
-      <c r="D59" s="3" t="n">
-        <v>-342068000</v>
-      </c>
       <c r="E59" s="3" t="n">
-        <v>-85798000</v>
+        <v>-432607000</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>-3622000</v>
+        <v>4741000</v>
       </c>
       <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7609,12 +9993,13 @@
       </c>
       <c r="B60" s="3" t="n"/>
       <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="n">
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n">
         <v>156000</v>
       </c>
-      <c r="E60" s="3" t="n"/>
       <c r="F60" s="3" t="n"/>
       <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7623,34 +10008,35 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
+        <v>-378343000</v>
+      </c>
+      <c r="C61" s="3" t="n">
         <v>-378711000</v>
       </c>
-      <c r="C61" s="3" t="n">
+      <c r="D61" s="3" t="n">
         <v>-925000</v>
       </c>
-      <c r="D61" s="3" t="n">
+      <c r="E61" s="3" t="n">
         <v>257390000</v>
       </c>
-      <c r="E61" s="3" t="n">
+      <c r="F61" s="3" t="n">
         <v>-138792000</v>
       </c>
-      <c r="F61" s="3" t="n">
-        <v>246791000</v>
-      </c>
       <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7681,6 +10067,18 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GAAP (statement) ~35% vs yfinance info.grossMargins 51% — info is a non-GAAP basis; FY Summary uses GAAP</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
